--- a/scraper/downloads/yad2_page_6.xlsx
+++ b/scraper/downloads/yad2_page_6.xlsx
@@ -333,60 +333,57 @@
       </c>
       <c t="inlineStr" r="C3">
         <is>
-          <t xml:space="preserve">ראובן</t>
+          <t xml:space="preserve">קרן היסוד</t>
         </is>
       </c>
       <c r="D3" s="65">
-        <v>16</v>
-      </c>
-      <c r="E3" s="65">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c t="inlineStr" r="E3">
+        <is>
+          <t xml:space="preserve">/32</t>
+        </is>
       </c>
       <c t="inlineStr" r="F3">
         <is>
-          <t xml:space="preserve">דירת גן</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c r="G3" s="65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="H3">
         <is>
-          <t xml:space="preserve">125מ״ר</t>
+          <t xml:space="preserve">70מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I3">
         <is>
-          <t xml:space="preserve">גינה: 40מ״ר</t>
+          <t xml:space="preserve">מרפסת: 8מ״רמרפסת: 7מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J3">
         <is>
-          <t xml:space="preserve">1חניות</t>
+          <t xml:space="preserve">ללא חניה</t>
         </is>
       </c>
       <c t="inlineStr" r="K3">
         <is>
-          <t xml:space="preserve">יש מחסן</t>
+          <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
       <c t="inlineStr" r="L3">
         <is>
-          <t xml:space="preserve">דרום מערב</t>
+          <t xml:space="preserve">צפון דרום מזרח</t>
         </is>
       </c>
       <c t="inlineStr" r="N3">
         <is>
-          <t xml:space="preserve">משה קליין58-716-1160⁩0</t>
+          <t xml:space="preserve">סיימון סינגר</t>
         </is>
       </c>
       <c r="O3" s="63">
-        <v>10800000</v>
-      </c>
-      <c t="inlineStr" r="P3">
-        <is>
-          <t xml:space="preserve">בלעדיות</t>
-        </is>
+        <v>4300000</v>
       </c>
       <c t="inlineStr" r="R3">
         <is>
@@ -395,7 +392,7 @@
       </c>
       <c t="inlineStr" r="S3">
         <is>
-          <t xml:space="preserve">אורן כהן08-06-2026</t>
+          <t xml:space="preserve">מיכאל בלוך31-10-2024</t>
         </is>
       </c>
     </row>
@@ -410,33 +407,31 @@
       </c>
       <c t="inlineStr" r="C4">
         <is>
-          <t xml:space="preserve">רבדים</t>
+          <t xml:space="preserve">ראובן</t>
         </is>
       </c>
       <c r="D4" s="65">
-        <v>6</v>
-      </c>
-      <c t="inlineStr" r="E4">
-        <is>
-          <t xml:space="preserve">/40</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="E4" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F4">
         <is>
           <t xml:space="preserve">דירת גן</t>
         </is>
       </c>
-      <c t="n" r="G4">
-        <v>4.5</v>
+      <c r="G4" s="65">
+        <v>4</v>
       </c>
       <c t="inlineStr" r="H4">
         <is>
-          <t xml:space="preserve">138.4מ״ר</t>
+          <t xml:space="preserve">125מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I4">
         <is>
-          <t xml:space="preserve">מרפסת: 12.3מ״רמרפסת: 1.1מ״רמרפסת: 1.1מ״רגינה: 24.3מ״ר</t>
+          <t xml:space="preserve">גינה: 40מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J4">
@@ -451,21 +446,21 @@
       </c>
       <c t="inlineStr" r="L4">
         <is>
-          <t xml:space="preserve">דרום מזרח מערב</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="M4">
-        <is>
-          <t xml:space="preserve">חזית עורף</t>
+          <t xml:space="preserve">דרום מערב</t>
         </is>
       </c>
       <c t="inlineStr" r="N4">
         <is>
-          <t xml:space="preserve">אורית סטרולביץ(052) 223-2066</t>
+          <t xml:space="preserve">משה קליין58-716-1160⁩0</t>
         </is>
       </c>
       <c r="O4" s="63">
-        <v>5695000</v>
+        <v>10800000</v>
+      </c>
+      <c t="inlineStr" r="P4">
+        <is>
+          <t xml:space="preserve">בלעדיות</t>
+        </is>
       </c>
       <c t="inlineStr" r="R4">
         <is>
@@ -474,7 +469,7 @@
       </c>
       <c t="inlineStr" r="S4">
         <is>
-          <t xml:space="preserve">אריה טאו21-09-2025</t>
+          <t xml:space="preserve">אורן כהן08-06-2026</t>
         </is>
       </c>
     </row>
@@ -489,45 +484,62 @@
       </c>
       <c t="inlineStr" r="C5">
         <is>
-          <t xml:space="preserve">רבי חלפתא</t>
+          <t xml:space="preserve">רבדים</t>
         </is>
       </c>
       <c r="D5" s="65">
-        <v>5</v>
-      </c>
-      <c r="E5" s="65">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c t="inlineStr" r="E5">
+        <is>
+          <t xml:space="preserve">/40</t>
+        </is>
       </c>
       <c t="inlineStr" r="F5">
         <is>
-          <t xml:space="preserve">דירה</t>
-        </is>
-      </c>
-      <c r="G5" s="65">
-        <v>3</v>
+          <t xml:space="preserve">דירת גן</t>
+        </is>
+      </c>
+      <c t="n" r="G5">
+        <v>4.5</v>
       </c>
       <c t="inlineStr" r="H5">
         <is>
-          <t xml:space="preserve">95מ״ר</t>
+          <t xml:space="preserve">138.4מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I5">
+        <is>
+          <t xml:space="preserve">מרפסת: 12.3מ״רמרפסת: 1.1מ״רמרפסת: 1.1מ״רגינה: 24.3מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J5">
         <is>
-          <t xml:space="preserve">ללא חניה</t>
+          <t xml:space="preserve">1חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K5">
         <is>
-          <t xml:space="preserve">ללא מחסן</t>
+          <t xml:space="preserve">יש מחסן</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="L5">
+        <is>
+          <t xml:space="preserve">דרום מזרח מערב</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="M5">
+        <is>
+          <t xml:space="preserve">חזית עורף</t>
         </is>
       </c>
       <c t="inlineStr" r="N5">
         <is>
-          <t xml:space="preserve">משה בלאייש</t>
-        </is>
-      </c>
-      <c r="O5" s="65">
-        <v>0</v>
+          <t xml:space="preserve">אורית סטרולביץ(052) 223-2066</t>
+        </is>
+      </c>
+      <c r="O5" s="63">
+        <v>5695000</v>
       </c>
       <c t="inlineStr" r="R5">
         <is>
@@ -536,7 +548,7 @@
       </c>
       <c t="inlineStr" r="S5">
         <is>
-          <t xml:space="preserve">רבקה בן זקן04-11-2024</t>
+          <t xml:space="preserve">אריה טאו21-09-2025</t>
         </is>
       </c>
     </row>
@@ -566,11 +578,11 @@
         </is>
       </c>
       <c r="G6" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="H6">
         <is>
-          <t xml:space="preserve">108מ״ר</t>
+          <t xml:space="preserve">95מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J6">
@@ -585,7 +597,7 @@
       </c>
       <c t="inlineStr" r="N6">
         <is>
-          <t xml:space="preserve">בלאייש משה</t>
+          <t xml:space="preserve">משה בלאייש</t>
         </is>
       </c>
       <c r="O6" s="65">
@@ -624,15 +636,15 @@
       </c>
       <c t="inlineStr" r="F7">
         <is>
-          <t xml:space="preserve">דירת גן</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c r="G7" s="65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="H7">
         <is>
-          <t xml:space="preserve">180מ״ר</t>
+          <t xml:space="preserve">108מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J7">
@@ -647,7 +659,7 @@
       </c>
       <c t="inlineStr" r="N7">
         <is>
-          <t xml:space="preserve">משה בלאייש</t>
+          <t xml:space="preserve">בלאייש משה</t>
         </is>
       </c>
       <c r="O7" s="65">
@@ -690,11 +702,11 @@
         </is>
       </c>
       <c r="G8" s="65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c t="inlineStr" r="H8">
         <is>
-          <t xml:space="preserve">159מ״ר</t>
+          <t xml:space="preserve">180מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J8">
@@ -748,15 +760,15 @@
       </c>
       <c t="inlineStr" r="F9">
         <is>
-          <t xml:space="preserve">דירה</t>
+          <t xml:space="preserve">דירת גן</t>
         </is>
       </c>
       <c r="G9" s="65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c t="inlineStr" r="H9">
         <is>
-          <t xml:space="preserve">97מ״ר</t>
+          <t xml:space="preserve">159מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J9">
@@ -799,36 +811,31 @@
       </c>
       <c t="inlineStr" r="C10">
         <is>
-          <t xml:space="preserve">רבי עקיבא</t>
+          <t xml:space="preserve">רבי חלפתא</t>
         </is>
       </c>
       <c r="D10" s="65">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E10" s="65">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F10">
         <is>
-          <t xml:space="preserve">פנטהאוז</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c r="G10" s="65">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="H10">
         <is>
-          <t xml:space="preserve">253מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I10">
-        <is>
-          <t xml:space="preserve">מרפסת: 70מ״ר</t>
+          <t xml:space="preserve">97מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J10">
         <is>
-          <t xml:space="preserve">1חניות</t>
+          <t xml:space="preserve">ללא חניה</t>
         </is>
       </c>
       <c t="inlineStr" r="K10">
@@ -836,18 +843,13 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="L10">
-        <is>
-          <t xml:space="preserve">צפון דרום מזרח מערב</t>
-        </is>
-      </c>
-      <c r="O10" s="63">
-        <v>21000000</v>
-      </c>
-      <c t="inlineStr" r="P10">
-        <is>
-          <t xml:space="preserve">ריהוטמשופצת</t>
-        </is>
+      <c t="inlineStr" r="N10">
+        <is>
+          <t xml:space="preserve">משה בלאייש</t>
+        </is>
+      </c>
+      <c r="O10" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R10">
         <is>
@@ -856,7 +858,7 @@
       </c>
       <c t="inlineStr" r="S10">
         <is>
-          <t xml:space="preserve">אורן כהן26-08-2024</t>
+          <t xml:space="preserve">רבקה בן זקן04-11-2024</t>
         </is>
       </c>
     </row>
@@ -871,31 +873,36 @@
       </c>
       <c t="inlineStr" r="C11">
         <is>
-          <t xml:space="preserve">רד"ק</t>
+          <t xml:space="preserve">רבי עקיבא</t>
         </is>
       </c>
       <c r="D11" s="65">
         <v>12</v>
       </c>
       <c r="E11" s="65">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c t="inlineStr" r="F11">
         <is>
-          <t xml:space="preserve">דירה</t>
+          <t xml:space="preserve">פנטהאוז</t>
         </is>
       </c>
       <c r="G11" s="65">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c t="inlineStr" r="H11">
         <is>
-          <t xml:space="preserve">124מ״ר</t>
+          <t xml:space="preserve">253מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I11">
+        <is>
+          <t xml:space="preserve">מרפסת: 70מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J11">
         <is>
-          <t xml:space="preserve">ללא חניה</t>
+          <t xml:space="preserve">1חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K11">
@@ -903,13 +910,18 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="N11">
-        <is>
-          <t xml:space="preserve">ברוך בלוי(052) 678-9111</t>
-        </is>
-      </c>
-      <c r="O11" s="65">
-        <v>0</v>
+      <c t="inlineStr" r="L11">
+        <is>
+          <t xml:space="preserve">צפון דרום מזרח מערב</t>
+        </is>
+      </c>
+      <c r="O11" s="63">
+        <v>21000000</v>
+      </c>
+      <c t="inlineStr" r="P11">
+        <is>
+          <t xml:space="preserve">ריהוטמשופצת</t>
+        </is>
       </c>
       <c t="inlineStr" r="R11">
         <is>
@@ -918,7 +930,7 @@
       </c>
       <c t="inlineStr" r="S11">
         <is>
-          <t xml:space="preserve">רבקה בן זקן04-11-2024</t>
+          <t xml:space="preserve">אורן כהן26-08-2024</t>
         </is>
       </c>
     </row>
@@ -937,7 +949,7 @@
         </is>
       </c>
       <c r="D12" s="65">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E12" s="65">
         <v>0</v>
@@ -948,11 +960,11 @@
         </is>
       </c>
       <c r="G12" s="65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c t="inlineStr" r="H12">
         <is>
-          <t xml:space="preserve">157מ״ר</t>
+          <t xml:space="preserve">124מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J12">
@@ -967,7 +979,7 @@
       </c>
       <c t="inlineStr" r="N12">
         <is>
-          <t xml:space="preserve">אינווסט קפיטל(054) 397-4100</t>
+          <t xml:space="preserve">ברוך בלוי(052) 678-9111</t>
         </is>
       </c>
       <c r="O12" s="65">
@@ -980,7 +992,7 @@
       </c>
       <c t="inlineStr" r="S12">
         <is>
-          <t xml:space="preserve">משה קולטון04-11-2024</t>
+          <t xml:space="preserve">רבקה בן זקן04-11-2024</t>
         </is>
       </c>
     </row>
@@ -999,12 +1011,10 @@
         </is>
       </c>
       <c r="D13" s="65">
-        <v>19</v>
-      </c>
-      <c t="inlineStr" r="E13">
-        <is>
-          <t xml:space="preserve">/54</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="E13" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F13">
         <is>
@@ -1012,35 +1022,30 @@
         </is>
       </c>
       <c r="G13" s="65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c t="inlineStr" r="H13">
         <is>
-          <t xml:space="preserve">99.6מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I13">
-        <is>
-          <t xml:space="preserve">מרפסת: 3.6מ״ר</t>
+          <t xml:space="preserve">157מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J13">
         <is>
-          <t xml:space="preserve">1חניות</t>
+          <t xml:space="preserve">ללא חניה</t>
         </is>
       </c>
       <c t="inlineStr" r="K13">
         <is>
-          <t xml:space="preserve">יש מחסן</t>
+          <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
       <c t="inlineStr" r="N13">
         <is>
-          <t xml:space="preserve">אוליבייה איינס+972 54-445-3046</t>
-        </is>
-      </c>
-      <c r="O13" s="63">
-        <v>6600000</v>
+          <t xml:space="preserve">אינווסט קפיטל(054) 397-4100</t>
+        </is>
+      </c>
+      <c r="O13" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R13">
         <is>
@@ -1049,7 +1054,7 @@
       </c>
       <c t="inlineStr" r="S13">
         <is>
-          <t xml:space="preserve">יניב אשכנזי29-06-2025</t>
+          <t xml:space="preserve">משה קולטון04-11-2024</t>
         </is>
       </c>
     </row>
@@ -1064,14 +1069,16 @@
       </c>
       <c t="inlineStr" r="C14">
         <is>
-          <t xml:space="preserve">רחל אמנו</t>
+          <t xml:space="preserve">רד"ק</t>
         </is>
       </c>
       <c r="D14" s="65">
-        <v>17</v>
-      </c>
-      <c r="E14" s="65">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c t="inlineStr" r="E14">
+        <is>
+          <t xml:space="preserve">/54</t>
+        </is>
       </c>
       <c t="inlineStr" r="F14">
         <is>
@@ -1079,35 +1086,35 @@
         </is>
       </c>
       <c r="G14" s="65">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c t="inlineStr" r="H14">
         <is>
-          <t xml:space="preserve">451מ״ר</t>
+          <t xml:space="preserve">99.6מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I14">
         <is>
-          <t xml:space="preserve">מרפסת: 47מ״ר</t>
+          <t xml:space="preserve">מרפסת: 3.6מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J14">
         <is>
-          <t xml:space="preserve">ללא חניה</t>
+          <t xml:space="preserve">1חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K14">
         <is>
-          <t xml:space="preserve">ללא מחסן</t>
+          <t xml:space="preserve">יש מחסן</t>
         </is>
       </c>
       <c t="inlineStr" r="N14">
         <is>
-          <t xml:space="preserve">פיינגולד שמואל</t>
-        </is>
-      </c>
-      <c r="O14" s="65">
-        <v>0</v>
+          <t xml:space="preserve">אוליבייה איינס+972 54-445-3046</t>
+        </is>
+      </c>
+      <c r="O14" s="63">
+        <v>6600000</v>
       </c>
       <c t="inlineStr" r="R14">
         <is>
@@ -1116,7 +1123,7 @@
       </c>
       <c t="inlineStr" r="S14">
         <is>
-          <t xml:space="preserve">אורן כהן04-11-2024</t>
+          <t xml:space="preserve">יניב אשכנזי29-06-2025</t>
         </is>
       </c>
     </row>
@@ -1138,24 +1145,24 @@
         <v>17</v>
       </c>
       <c r="E15" s="65">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F15">
         <is>
-          <t xml:space="preserve">פנטהאוז</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c r="G15" s="65">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="H15">
         <is>
-          <t xml:space="preserve">195מ״ר</t>
+          <t xml:space="preserve">451מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I15">
         <is>
-          <t xml:space="preserve">מרפסת: 38מ״ר</t>
+          <t xml:space="preserve">מרפסת: 47מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J15">
@@ -1170,7 +1177,7 @@
       </c>
       <c t="inlineStr" r="N15">
         <is>
-          <t xml:space="preserve">פיינגולד שמואל(052) 240-8532</t>
+          <t xml:space="preserve">פיינגולד שמואל</t>
         </is>
       </c>
       <c r="O15" s="65">
@@ -1198,26 +1205,31 @@
       </c>
       <c t="inlineStr" r="C16">
         <is>
-          <t xml:space="preserve">רמב"ן</t>
+          <t xml:space="preserve">רחל אמנו</t>
         </is>
       </c>
       <c r="D16" s="65">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E16" s="65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="F16">
         <is>
-          <t xml:space="preserve">דירה</t>
+          <t xml:space="preserve">פנטהאוז</t>
         </is>
       </c>
       <c r="G16" s="65">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c t="inlineStr" r="H16">
         <is>
-          <t xml:space="preserve">0מ״ר</t>
+          <t xml:space="preserve">195מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I16">
+        <is>
+          <t xml:space="preserve">מרפסת: 38מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J16">
@@ -1232,7 +1244,7 @@
       </c>
       <c t="inlineStr" r="N16">
         <is>
-          <t xml:space="preserve">לפרסום לא</t>
+          <t xml:space="preserve">פיינגולד שמואל(052) 240-8532</t>
         </is>
       </c>
       <c r="O16" s="65">
@@ -1264,14 +1276,14 @@
         </is>
       </c>
       <c r="D17" s="65">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E17" s="65">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F17">
         <is>
-          <t xml:space="preserve">בית פרטי</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c r="G17" s="65">
@@ -1279,7 +1291,7 @@
       </c>
       <c t="inlineStr" r="H17">
         <is>
-          <t xml:space="preserve">450מ״ר</t>
+          <t xml:space="preserve">0מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J17">
@@ -1294,11 +1306,11 @@
       </c>
       <c t="inlineStr" r="N17">
         <is>
-          <t xml:space="preserve">עובדיה הדאיה052-5583677Ovadya1246@gmail.com</t>
-        </is>
-      </c>
-      <c r="O17" s="63">
-        <v>60000000</v>
+          <t xml:space="preserve">לפרסום לא</t>
+        </is>
+      </c>
+      <c r="O17" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R17">
         <is>
@@ -1307,7 +1319,7 @@
       </c>
       <c t="inlineStr" r="S17">
         <is>
-          <t xml:space="preserve">אורן כהן22-05-2025</t>
+          <t xml:space="preserve">אורן כהן04-11-2024</t>
         </is>
       </c>
     </row>
@@ -1322,33 +1334,26 @@
       </c>
       <c t="inlineStr" r="C18">
         <is>
-          <t xml:space="preserve">רמבן</t>
+          <t xml:space="preserve">רמב"ן</t>
         </is>
       </c>
       <c r="D18" s="65">
-        <v>37</v>
-      </c>
-      <c t="inlineStr" r="E18">
-        <is>
-          <t xml:space="preserve">/31</t>
-        </is>
+        <v>33</v>
+      </c>
+      <c r="E18" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F18">
         <is>
-          <t xml:space="preserve">דירה</t>
-        </is>
-      </c>
-      <c t="n" r="G18">
-        <v>4.5</v>
+          <t xml:space="preserve">בית פרטי</t>
+        </is>
+      </c>
+      <c r="G18" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="H18">
         <is>
-          <t xml:space="preserve">137מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I18">
-        <is>
-          <t xml:space="preserve">מרפסת: 30מ״ר</t>
+          <t xml:space="preserve">450מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J18">
@@ -1361,23 +1366,13 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="L18">
-        <is>
-          <t xml:space="preserve">צפון דרום מזרח מערב</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="M18">
-        <is>
-          <t xml:space="preserve">חזית עורף</t>
-        </is>
-      </c>
       <c t="inlineStr" r="N18">
         <is>
-          <t xml:space="preserve">מגי שקי(052) 368-1454אורי שקי (בן)(052) 946-4597</t>
+          <t xml:space="preserve">עובדיה הדאיה052-5583677Ovadya1246@gmail.com</t>
         </is>
       </c>
       <c r="O18" s="63">
-        <v>16000</v>
+        <v>60000000</v>
       </c>
       <c t="inlineStr" r="R18">
         <is>
@@ -1386,7 +1381,7 @@
       </c>
       <c t="inlineStr" r="S18">
         <is>
-          <t xml:space="preserve">אריה טאו04-06-2026</t>
+          <t xml:space="preserve">אורן כהן22-05-2025</t>
         </is>
       </c>
     </row>
@@ -1405,11 +1400,11 @@
         </is>
       </c>
       <c r="D19" s="65">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c t="inlineStr" r="E19">
         <is>
-          <t xml:space="preserve">/44</t>
+          <t xml:space="preserve">/31</t>
         </is>
       </c>
       <c t="inlineStr" r="F19">
@@ -1417,17 +1412,17 @@
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
-      <c r="G19" s="65">
-        <v>2</v>
+      <c t="n" r="G19">
+        <v>4.5</v>
       </c>
       <c t="inlineStr" r="H19">
         <is>
-          <t xml:space="preserve">50מ״ר</t>
+          <t xml:space="preserve">137מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I19">
         <is>
-          <t xml:space="preserve">מרפסת: 18מ״ר</t>
+          <t xml:space="preserve">מרפסת: 30מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J19">
@@ -1442,16 +1437,21 @@
       </c>
       <c t="inlineStr" r="L19">
         <is>
-          <t xml:space="preserve">צפון מערב</t>
+          <t xml:space="preserve">צפון דרום מזרח מערב</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="M19">
+        <is>
+          <t xml:space="preserve">חזית עורף</t>
         </is>
       </c>
       <c t="inlineStr" r="N19">
         <is>
-          <t xml:space="preserve">דוד דוויד(054) 683-7359</t>
+          <t xml:space="preserve">מגי שקי(052) 368-1454אורי שקי (בן)(052) 946-4597</t>
         </is>
       </c>
       <c r="O19" s="63">
-        <v>3800000</v>
+        <v>16000</v>
       </c>
       <c t="inlineStr" r="R19">
         <is>
@@ -1460,7 +1460,7 @@
       </c>
       <c t="inlineStr" r="S19">
         <is>
-          <t xml:space="preserve">דוב רבינובץ\'12-05-2026</t>
+          <t xml:space="preserve">אריה טאו04-06-2026</t>
         </is>
       </c>
     </row>
@@ -1475,14 +1475,16 @@
       </c>
       <c t="inlineStr" r="C20">
         <is>
-          <t xml:space="preserve">רמה</t>
+          <t xml:space="preserve">רמבן</t>
         </is>
       </c>
       <c r="D20" s="65">
-        <v>0</v>
-      </c>
-      <c r="E20" s="65">
-        <v>0</v>
+        <v>59</v>
+      </c>
+      <c t="inlineStr" r="E20">
+        <is>
+          <t xml:space="preserve">/44</t>
+        </is>
       </c>
       <c t="inlineStr" r="F20">
         <is>
@@ -1490,11 +1492,16 @@
         </is>
       </c>
       <c r="G20" s="65">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="H20">
         <is>
-          <t xml:space="preserve">300מ״ר</t>
+          <t xml:space="preserve">50מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I20">
+        <is>
+          <t xml:space="preserve">מרפסת: 18מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J20">
@@ -1507,13 +1514,18 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
+      <c t="inlineStr" r="L20">
+        <is>
+          <t xml:space="preserve">צפון מערב</t>
+        </is>
+      </c>
       <c t="inlineStr" r="N20">
         <is>
-          <t xml:space="preserve">יהודה סרגה</t>
-        </is>
-      </c>
-      <c r="O20" s="65">
-        <v>0</v>
+          <t xml:space="preserve">דוד דוויד(054) 683-7359</t>
+        </is>
+      </c>
+      <c r="O20" s="63">
+        <v>3800000</v>
       </c>
       <c t="inlineStr" r="R20">
         <is>
@@ -1522,7 +1534,7 @@
       </c>
       <c t="inlineStr" r="S20">
         <is>
-          <t xml:space="preserve">רבקה בן זקן04-11-2024</t>
+          <t xml:space="preserve">דוב רבינובץ\'12-05-2026</t>
         </is>
       </c>
     </row>
@@ -1541,22 +1553,22 @@
         </is>
       </c>
       <c r="D21" s="65">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E21" s="65">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F21">
         <is>
-          <t xml:space="preserve">בית פרטי</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c r="G21" s="65">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c t="inlineStr" r="H21">
         <is>
-          <t xml:space="preserve">228מ״ר</t>
+          <t xml:space="preserve">300מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J21">
@@ -1569,23 +1581,13 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="L21">
-        <is>
-          <t xml:space="preserve">צפון</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="M21">
-        <is>
-          <t xml:space="preserve">חזית</t>
-        </is>
-      </c>
       <c t="inlineStr" r="N21">
         <is>
-          <t xml:space="preserve">נתנאל גיאתדב בלוי(052) 841-2127</t>
-        </is>
-      </c>
-      <c r="O21" s="63">
-        <v>7500000</v>
+          <t xml:space="preserve">יהודה סרגה</t>
+        </is>
+      </c>
+      <c r="O21" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R21">
         <is>
@@ -1594,7 +1596,7 @@
       </c>
       <c t="inlineStr" r="S21">
         <is>
-          <t xml:space="preserve">אריה טאו31-12-2025</t>
+          <t xml:space="preserve">רבקה בן זקן04-11-2024</t>
         </is>
       </c>
     </row>
@@ -1609,18 +1611,18 @@
       </c>
       <c t="inlineStr" r="C22">
         <is>
-          <t xml:space="preserve">רשבא</t>
+          <t xml:space="preserve">רמה</t>
         </is>
       </c>
       <c r="D22" s="65">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E22" s="65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F22">
         <is>
-          <t xml:space="preserve">דירה</t>
+          <t xml:space="preserve">בית פרטי</t>
         </is>
       </c>
       <c r="G22" s="65">
@@ -1628,17 +1630,12 @@
       </c>
       <c t="inlineStr" r="H22">
         <is>
-          <t xml:space="preserve">170מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I22">
-        <is>
-          <t xml:space="preserve">מרפסת: 10מ״רמרפסת: 5מ״רמרפסת: 3מ״ר</t>
+          <t xml:space="preserve">228מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J22">
         <is>
-          <t xml:space="preserve">1חניות</t>
+          <t xml:space="preserve">ללא חניה</t>
         </is>
       </c>
       <c t="inlineStr" r="K22">
@@ -1646,8 +1643,23 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
+      <c t="inlineStr" r="L22">
+        <is>
+          <t xml:space="preserve">צפון</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="M22">
+        <is>
+          <t xml:space="preserve">חזית</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="N22">
+        <is>
+          <t xml:space="preserve">נתנאל גיאתדב בלוי(052) 841-2127</t>
+        </is>
+      </c>
       <c r="O22" s="63">
-        <v>16500000</v>
+        <v>7500000</v>
       </c>
       <c t="inlineStr" r="R22">
         <is>
@@ -1656,7 +1668,7 @@
       </c>
       <c t="inlineStr" r="S22">
         <is>
-          <t xml:space="preserve">רבקה בן זקן15-02-2026</t>
+          <t xml:space="preserve">אריה טאו31-12-2025</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1683,11 @@
       </c>
       <c t="inlineStr" r="C23">
         <is>
-          <t xml:space="preserve">שדרות בן מיימון</t>
+          <t xml:space="preserve">רשבא</t>
         </is>
       </c>
       <c r="D23" s="65">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="E23" s="65">
         <v>1</v>
@@ -1690,17 +1702,17 @@
       </c>
       <c t="inlineStr" r="H23">
         <is>
-          <t xml:space="preserve">190מ״ר</t>
+          <t xml:space="preserve">170מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I23">
         <is>
-          <t xml:space="preserve">מרפסת: 60מ״ר</t>
+          <t xml:space="preserve">מרפסת: 10מ״רמרפסת: 5מ״רמרפסת: 3מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J23">
         <is>
-          <t xml:space="preserve">ללא חניה</t>
+          <t xml:space="preserve">1חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K23">
@@ -1708,13 +1720,8 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="N23">
-        <is>
-          <t xml:space="preserve">קפיטל</t>
-        </is>
-      </c>
-      <c r="O23" s="65">
-        <v>0</v>
+      <c r="O23" s="63">
+        <v>16500000</v>
       </c>
       <c t="inlineStr" r="R23">
         <is>
@@ -1723,7 +1730,7 @@
       </c>
       <c t="inlineStr" r="S23">
         <is>
-          <t xml:space="preserve">אורן כהן04-11-2024</t>
+          <t xml:space="preserve">רבקה בן זקן15-02-2026</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1752,7 @@
         <v>52</v>
       </c>
       <c r="E24" s="65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F24">
         <is>
@@ -1757,12 +1764,12 @@
       </c>
       <c t="inlineStr" r="H24">
         <is>
-          <t xml:space="preserve">199מ״ר</t>
+          <t xml:space="preserve">190מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I24">
         <is>
-          <t xml:space="preserve">מרפסת: 41מ״ר</t>
+          <t xml:space="preserve">מרפסת: 60מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J24">
@@ -1805,16 +1812,14 @@
       </c>
       <c t="inlineStr" r="C25">
         <is>
-          <t xml:space="preserve">שדרות בן צבי</t>
+          <t xml:space="preserve">שדרות בן מיימון</t>
         </is>
       </c>
       <c r="D25" s="65">
-        <v>31</v>
-      </c>
-      <c t="inlineStr" r="E25">
-        <is>
-          <t xml:space="preserve">/32</t>
-        </is>
+        <v>52</v>
+      </c>
+      <c r="E25" s="65">
+        <v>2</v>
       </c>
       <c t="inlineStr" r="F25">
         <is>
@@ -1822,11 +1827,16 @@
         </is>
       </c>
       <c r="G25" s="65">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="H25">
         <is>
-          <t xml:space="preserve">41מ״ר</t>
+          <t xml:space="preserve">199מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I25">
+        <is>
+          <t xml:space="preserve">מרפסת: 41מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J25">
@@ -1839,23 +1849,13 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="L25">
-        <is>
-          <t xml:space="preserve">דרום</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="M25">
-        <is>
-          <t xml:space="preserve">עורף</t>
-        </is>
-      </c>
       <c t="inlineStr" r="N25">
         <is>
-          <t xml:space="preserve">שמואל וינגורט(050) 540-9188</t>
-        </is>
-      </c>
-      <c r="O25" s="63">
-        <v>2400000</v>
+          <t xml:space="preserve">קפיטל</t>
+        </is>
+      </c>
+      <c r="O25" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R25">
         <is>
@@ -1864,7 +1864,7 @@
       </c>
       <c t="inlineStr" r="S25">
         <is>
-          <t xml:space="preserve">מנחם אוריאל04-09-2025</t>
+          <t xml:space="preserve">אורן כהן04-11-2024</t>
         </is>
       </c>
     </row>
@@ -1879,14 +1879,16 @@
       </c>
       <c t="inlineStr" r="C26">
         <is>
-          <t xml:space="preserve">שדרות ש''י עגנון</t>
+          <t xml:space="preserve">שדרות בן צבי</t>
         </is>
       </c>
       <c r="D26" s="65">
-        <v>11</v>
-      </c>
-      <c r="E26" s="65">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c t="inlineStr" r="E26">
+        <is>
+          <t xml:space="preserve">/32</t>
+        </is>
       </c>
       <c t="inlineStr" r="F26">
         <is>
@@ -1894,11 +1896,11 @@
         </is>
       </c>
       <c r="G26" s="65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="H26">
         <is>
-          <t xml:space="preserve">0מ״ר</t>
+          <t xml:space="preserve">41מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J26">
@@ -1911,13 +1913,23 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
+      <c t="inlineStr" r="L26">
+        <is>
+          <t xml:space="preserve">דרום</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="M26">
+        <is>
+          <t xml:space="preserve">עורף</t>
+        </is>
+      </c>
       <c t="inlineStr" r="N26">
         <is>
-          <t xml:space="preserve">Prosperity</t>
-        </is>
-      </c>
-      <c r="O26" s="65">
-        <v>0</v>
+          <t xml:space="preserve">שמואל וינגורט(050) 540-9188</t>
+        </is>
+      </c>
+      <c r="O26" s="63">
+        <v>2400000</v>
       </c>
       <c t="inlineStr" r="R26">
         <is>
@@ -1926,7 +1938,7 @@
       </c>
       <c t="inlineStr" r="S26">
         <is>
-          <t xml:space="preserve">אורן כהן04-11-2024</t>
+          <t xml:space="preserve">מנחם אוריאל04-09-2025</t>
         </is>
       </c>
     </row>
@@ -1941,11 +1953,11 @@
       </c>
       <c t="inlineStr" r="C27">
         <is>
-          <t xml:space="preserve">שופט חיים כהן</t>
+          <t xml:space="preserve">שדרות ש''י עגנון</t>
         </is>
       </c>
       <c r="D27" s="65">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E27" s="65">
         <v>0</v>
@@ -1956,30 +1968,30 @@
         </is>
       </c>
       <c r="G27" s="65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="H27">
         <is>
-          <t xml:space="preserve">80מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I27">
-        <is>
-          <t xml:space="preserve">מרפסת: 5מ״ר</t>
+          <t xml:space="preserve">0מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J27">
         <is>
-          <t xml:space="preserve">1חניות</t>
+          <t xml:space="preserve">ללא חניה</t>
         </is>
       </c>
       <c t="inlineStr" r="K27">
         <is>
-          <t xml:space="preserve">יש מחסן</t>
-        </is>
-      </c>
-      <c r="O27" s="63">
-        <v>3100000</v>
+          <t xml:space="preserve">ללא מחסן</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="N27">
+        <is>
+          <t xml:space="preserve">Prosperity</t>
+        </is>
+      </c>
+      <c r="O27" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R27">
         <is>
@@ -1988,7 +2000,7 @@
       </c>
       <c t="inlineStr" r="S27">
         <is>
-          <t xml:space="preserve">דוב רבינובץ\'31-05-2026</t>
+          <t xml:space="preserve">אורן כהן04-11-2024</t>
         </is>
       </c>
     </row>
